--- a/data/trans_dic/IP25-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP25-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -504,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -518,15 +519,12 @@
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que ven la televisión todos o casi todos los días</t>
+          <t>Menores que ven la televisión todos o casi todos los días (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -537,23 +535,20 @@
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Niño</t>
         </is>
       </c>
+      <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -575,47 +570,32 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
           <t>2007</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>2012</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>2016</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
         </is>
       </c>
     </row>
@@ -631,9 +611,6 @@
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
       <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -663,47 +640,32 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>94,15%</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
           <t>92,4%</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -716,62 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>87,76; 96,45</t>
+          <t>87,85; 96,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>88,85; 97,1</t>
+          <t>88,24; 97,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>81,61; 94,1</t>
+          <t>81,18; 94,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,74</t>
+          <t>82,41; 93,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>83,32; 94,03</t>
+          <t>89,01; 97,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,07; 97,49</t>
+          <t>89,04; 98,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,16; 98,22</t>
+          <t>87,29; 94,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,28</t>
+          <t>90,6; 96,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>87,24; 93,93</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>90,68; 96,74</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>88,3; 95,75</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0; 1,25</t>
+          <t>87,75; 95,42</t>
         </is>
       </c>
     </row>
@@ -803,47 +750,32 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>90,0%</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
           <t>91,9%</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -856,62 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>88,5; 93,15</t>
+          <t>88,64; 93,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>85,54; 90,3</t>
+          <t>85,4; 90,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>89,04; 93,14</t>
+          <t>89,02; 93,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,3</t>
+          <t>86,45; 91,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>86,2; 90,93</t>
+          <t>89,44; 93,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>89,37; 93,89</t>
+          <t>90,32; 94,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>90,13; 94,28</t>
+          <t>87,98; 91,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,29</t>
+          <t>88,23; 91,63</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>88,14; 91,29</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>88,22; 91,57</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>90,46; 93,23</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0; 0,15</t>
+          <t>90,47; 93,25</t>
         </is>
       </c>
     </row>
@@ -943,47 +860,32 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>88,65%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
           <t>86,49%</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -996,62 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>82,82; 90,77</t>
+          <t>82,34; 90,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>85,11; 92,91</t>
+          <t>85,2; 92,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>81,01; 90,08</t>
+          <t>81,43; 89,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,83</t>
+          <t>77,46; 87,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>77,31; 87,39</t>
+          <t>83,38; 91,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>83,0; 91,69</t>
+          <t>81,91; 90,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>82,34; 90,2</t>
+          <t>81,79; 88,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,8</t>
+          <t>85,93; 91,17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>81,94; 88,1</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>85,56; 91,32</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>83,56; 89,29</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>0; 0,41</t>
+          <t>83,56; 89,15</t>
         </is>
       </c>
     </row>
@@ -1083,47 +970,32 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>90,19%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
           <t>90,6%</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>88,22; 91,98</t>
+          <t>88,45; 92,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>87,15; 90,9</t>
+          <t>86,93; 90,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>88,05; 91,54</t>
+          <t>87,75; 91,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,2</t>
+          <t>85,44; 89,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>85,43; 89,35</t>
+          <t>89,55; 92,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,47; 92,95</t>
+          <t>89,47; 92,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,59; 92,99</t>
+          <t>87,42; 90,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,2</t>
+          <t>88,91; 91,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>87,43; 90,07</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>88,74; 91,46</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>89,26; 91,8</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0; 0,1</t>
+          <t>89,15; 91,76</t>
         </is>
       </c>
     </row>
@@ -1204,14 +1061,801 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A4:A5"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que ven la televisión todos o casi todos los días (tasa de respuesta: 99,89%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>84448</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>86686</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>53007</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>77482</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>81433</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>65254</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>161930</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>168119</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>118262</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>79824; 87613</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>81508; 89626</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>48202; 56157</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>71571; 81597</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>76722; 84209</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>61091; 67388</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>155120; 167339</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>161781; 172461</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>112309; 122126</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>573</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>639</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1209</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1222</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1288</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>378851</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>397142</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>430785</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>423358</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>451267</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>452361</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>802209</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>848408</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>883146</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>368828; 387835</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>385368; 407448</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>420414; 439453</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>412356; 434283</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>439533; 460236</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>441448; 460546</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>785718; 817449</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>831736; 863774</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>869461; 896185</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>424</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>458</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>150451</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>149054</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>148940</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>131063</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>151510</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>162599</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>281514</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>300565</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>311538</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>142143; 156735</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>142128; 154910</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>140625; 155304</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>122501; 137643</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>143606; 157969</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>153583; 169098</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>270513; 291745</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>291330; 309109</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>300971; 321128</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>915</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>909</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>948</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>971</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1865</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1886</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1919</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>613750</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>632881</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>632732</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>631903</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>684211</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>680214</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1245653</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1317092</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1312946</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>601092; 625225</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>617612; 645912</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>618103; 644853</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>616844; 645449</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>671495; 696835</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>666379; 691435</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>1225306; 1265460</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>1298305; 1336439</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>1292026; 1329840</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/trans_dic/IP25-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP25-Estudios-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>87,85; 96,42</t>
+          <t>87,04; 95,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>88,24; 97,03</t>
+          <t>88,75; 96,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>81,18; 94,58</t>
+          <t>81,68; 94,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>82,41; 93,96</t>
+          <t>82,47; 93,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>89,01; 97,7</t>
+          <t>89,6; 97,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,04; 98,21</t>
+          <t>88,79; 98,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,29; 94,16</t>
+          <t>87,32; 94,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>90,6; 96,58</t>
+          <t>90,64; 96,75</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>87,75; 95,42</t>
+          <t>87,66; 95,68</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>88,64; 93,21</t>
+          <t>88,89; 93,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>85,4; 90,29</t>
+          <t>85,34; 90,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>89,02; 93,05</t>
+          <t>88,96; 93,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>86,45; 91,05</t>
+          <t>86,46; 90,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>89,44; 93,65</t>
+          <t>89,45; 93,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>90,32; 94,23</t>
+          <t>90,59; 94,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>87,98; 91,53</t>
+          <t>88,09; 91,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>88,23; 91,63</t>
+          <t>88,35; 91,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>90,47; 93,25</t>
+          <t>90,47; 93,32</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>82,34; 90,8</t>
+          <t>82,64; 90,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>85,2; 92,87</t>
+          <t>84,84; 92,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>81,43; 89,93</t>
+          <t>81,32; 90,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>77,46; 87,04</t>
+          <t>77,54; 87,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>83,38; 91,72</t>
+          <t>83,38; 91,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>81,91; 90,19</t>
+          <t>82,42; 90,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>81,79; 88,2</t>
+          <t>81,93; 87,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>85,93; 91,17</t>
+          <t>85,38; 91,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>83,56; 89,15</t>
+          <t>83,48; 89,36</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>88,45; 92,0</t>
+          <t>88,33; 91,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>86,93; 90,92</t>
+          <t>87,07; 91,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>87,75; 91,55</t>
+          <t>87,83; 91,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>85,44; 89,4</t>
+          <t>85,27; 89,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>89,55; 92,93</t>
+          <t>89,5; 92,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,47; 92,83</t>
+          <t>89,44; 92,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,42; 90,29</t>
+          <t>87,49; 90,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>88,91; 91,52</t>
+          <t>88,94; 91,45</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>89,15; 91,76</t>
+          <t>89,31; 91,78</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>79824; 87613</t>
+          <t>79091; 87214</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>81508; 89626</t>
+          <t>81973; 89574</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>48202; 56157</t>
+          <t>48502; 56145</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>71571; 81597</t>
+          <t>71621; 81536</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>76722; 84209</t>
+          <t>77231; 84298</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>61091; 67388</t>
+          <t>60919; 67292</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>155120; 167339</t>
+          <t>155177; 167228</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>161781; 172461</t>
+          <t>161842; 172763</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>112309; 122126</t>
+          <t>112201; 122468</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>368828; 387835</t>
+          <t>369865; 387151</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>385368; 407448</t>
+          <t>385105; 407992</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>420414; 439453</t>
+          <t>420160; 439575</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>412356; 434283</t>
+          <t>412405; 434027</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>439533; 460236</t>
+          <t>439568; 460482</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>441448; 460546</t>
+          <t>442762; 461170</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>785718; 817449</t>
+          <t>786754; 815354</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>831736; 863774</t>
+          <t>832913; 862866</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>869461; 896185</t>
+          <t>869465; 896864</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>142143; 156735</t>
+          <t>142649; 157057</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>142128; 154910</t>
+          <t>141519; 155085</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>140625; 155304</t>
+          <t>140434; 155534</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>122501; 137643</t>
+          <t>122624; 137663</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>143606; 157969</t>
+          <t>143598; 157541</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>153583; 169098</t>
+          <t>154525; 169552</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>270513; 291745</t>
+          <t>271008; 290850</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>291330; 309109</t>
+          <t>289485; 308888</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>300971; 321128</t>
+          <t>300679; 321862</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>601092; 625225</t>
+          <t>600298; 625132</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>617612; 645912</t>
+          <t>618615; 646696</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>618103; 644853</t>
+          <t>618652; 644628</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>616844; 645449</t>
+          <t>615605; 644367</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>671495; 696835</t>
+          <t>671132; 696662</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>666379; 691435</t>
+          <t>666188; 691607</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1225306; 1265460</t>
+          <t>1226147; 1264345</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1298305; 1336439</t>
+          <t>1298752; 1335385</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1292026; 1329840</t>
+          <t>1294340; 1330065</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP25-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP25-Estudios-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>89,22%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>94,48%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>95,1%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>92,94%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>93,85%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>89,27%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>89,22%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>94,48%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>95,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>87,04; 95,98</t>
+          <t>83,32; 94,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>88,75; 96,97</t>
+          <t>89,07; 97,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>81,68; 94,56</t>
+          <t>89,16; 98,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>82,47; 93,89</t>
+          <t>87,76; 96,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>89,6; 97,8</t>
+          <t>88,85; 97,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,79; 98,07</t>
+          <t>81,61; 94,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,32; 94,1</t>
+          <t>87,24; 93,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>90,64; 96,75</t>
+          <t>90,68; 96,74</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>87,66; 95,68</t>
+          <t>88,3; 95,75</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>88,76%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>91,83%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>92,56%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>91,05%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>88,01%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>91,21%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>88,76%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>91,83%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>92,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>88,89; 93,05</t>
+          <t>86,2; 90,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>85,34; 90,41</t>
+          <t>89,37; 93,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>88,96; 93,07</t>
+          <t>90,13; 94,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>86,46; 90,99</t>
+          <t>88,5; 93,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>89,45; 93,7</t>
+          <t>85,54; 90,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>90,59; 94,36</t>
+          <t>89,04; 93,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>88,09; 91,3</t>
+          <t>88,14; 91,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>88,35; 91,53</t>
+          <t>88,22; 91,57</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>90,47; 93,32</t>
+          <t>90,46; 93,23</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>82,88%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>87,97%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>86,72%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>87,16%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>89,35%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>86,24%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>82,88%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>87,97%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>86,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>82,64; 90,98</t>
+          <t>77,31; 87,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>84,84; 92,97</t>
+          <t>83,0; 91,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>81,32; 90,06</t>
+          <t>82,34; 90,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>77,54; 87,05</t>
+          <t>82,82; 90,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>83,38; 91,47</t>
+          <t>85,11; 92,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>82,42; 90,43</t>
+          <t>81,01; 90,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>81,93; 87,93</t>
+          <t>81,94; 88,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>85,38; 91,11</t>
+          <t>85,56; 91,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>83,48; 89,36</t>
+          <t>83,56; 89,29</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>87,52%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>91,25%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>91,32%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>90,31%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>89,08%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>89,83%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>87,52%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>91,25%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>91,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>88,33; 91,99</t>
+          <t>85,43; 89,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>87,07; 91,03</t>
+          <t>89,47; 92,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>87,83; 91,52</t>
+          <t>89,59; 92,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>85,27; 89,25</t>
+          <t>88,22; 91,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>89,5; 92,91</t>
+          <t>87,15; 90,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,44; 92,85</t>
+          <t>88,05; 91,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,49; 90,21</t>
+          <t>87,43; 90,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>88,94; 91,45</t>
+          <t>88,74; 91,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>89,31; 91,78</t>
+          <t>89,26; 91,8</t>
         </is>
       </c>
     </row>
@@ -1105,14 +1105,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1200,32 +1200,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>126</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>79</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>77482</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>81433</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>65254</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>84448</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>86686</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>53007</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>77482</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>81433</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>65254</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>79091; 87214</t>
+          <t>72361; 81660</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>81973; 89574</t>
+          <t>76775; 84030</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>48502; 56145</t>
+          <t>61174; 67393</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>71621; 81536</t>
+          <t>79744; 87640</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>77231; 84298</t>
+          <t>82074; 89690</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>60919; 67292</t>
+          <t>48457; 55875</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>155177; 167228</t>
+          <t>155036; 166931</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>161842; 172763</t>
+          <t>161914; 172737</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>112201; 122468</t>
+          <t>113014; 122551</t>
         </is>
       </c>
     </row>
@@ -1363,32 +1363,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>639</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>570</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>573</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>646</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>639</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>649</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1416,32 +1416,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>423358</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>451267</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>452361</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>378851</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>397142</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>430785</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>423358</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>451267</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>452361</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>369865; 387151</t>
+          <t>411163; 433741</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>385105; 407992</t>
+          <t>439195; 461408</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>420160; 439575</t>
+          <t>440489; 460767</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>412405; 434027</t>
+          <t>368250; 387584</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>439568; 460482</t>
+          <t>386006; 407476</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>442762; 461170</t>
+          <t>420533; 439889</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>786754; 815354</t>
+          <t>787184; 815328</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>832913; 862866</t>
+          <t>831617; 863201</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>869465; 896864</t>
+          <t>869386; 895942</t>
         </is>
       </c>
     </row>
@@ -1526,32 +1526,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>210</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>223</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1579,32 +1579,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>131063</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>151510</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>162599</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>150451</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>149054</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>148940</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>131063</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>151510</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>162599</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>142649; 157057</t>
+          <t>122256; 138193</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>141519; 155085</t>
+          <t>142947; 157919</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>140434; 155534</t>
+          <t>154390; 169125</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>122624; 137663</t>
+          <t>142962; 156690</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>143598; 157541</t>
+          <t>141970; 154980</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>154525; 169552</t>
+          <t>139911; 155577</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>271008; 290850</t>
+          <t>271024; 291400</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>289485; 308888</t>
+          <t>290082; 309601</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>300679; 321862</t>
+          <t>300991; 321636</t>
         </is>
       </c>
     </row>
@@ -1689,32 +1689,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>971</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>909</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>948</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>950</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>971</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1742,32 +1742,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>631903</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>684211</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>680214</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>613750</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>632881</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>632732</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>631903</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>684211</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>680214</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>600298; 625132</t>
+          <t>616781; 645111</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>618615; 646696</t>
+          <t>670894; 696996</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>618652; 644628</t>
+          <t>667283; 692635</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>615605; 644367</t>
+          <t>599517; 625109</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>671132; 696662</t>
+          <t>619167; 645775</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>666188; 691607</t>
+          <t>620191; 644772</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1226147; 1264345</t>
+          <t>1225317; 1262420</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1298752; 1335385</t>
+          <t>1295802; 1335639</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1294340; 1330065</t>
+          <t>1293630; 1330342</t>
         </is>
       </c>
     </row>
